--- a/public/PICO_8_MASTER_OUTPUT.xlsx
+++ b/public/PICO_8_MASTER_OUTPUT.xlsx
@@ -854,9 +854,9 @@
 const DATA = {
   period: "Current Period",
   email: {
-    totalSends: 21,
-    avgOpenRate: 0.5371,
-    avgClickRate: 0.0301,
+    totalSends: 0,
+    avgOpenRate: 0,
+    avgClickRate: 0,
     listSize180DO: 0,
   },
   finances: {

--- a/public/PICO_8_MASTER_OUTPUT.xlsx
+++ b/public/PICO_8_MASTER_OUTPUT.xlsx
@@ -63,7 +63,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -110,11 +110,6 @@
         <fgColor rgb="00FFDDC1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFCCCC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -128,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -158,9 +153,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -538,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -592,7 +584,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Email performance across 5 period tabs. Rating formula grades each send on open rate.</t>
+          <t>Email performance. Rating formula grades each send on open rate.</t>
         </is>
       </c>
     </row>
@@ -604,7 +596,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Segment sizes + weekly history. Auto-calculates week-over-week change. Update weekly.</t>
+          <t>Segment sizes + weekly history. Auto-calculates week-over-week change.</t>
         </is>
       </c>
     </row>
@@ -616,7 +608,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>ActBlue monthly fundraising with digital breakdown. Tracks against 10% digital target.</t>
+          <t>ActBlue monthly fundraising with digital breakdown.</t>
         </is>
       </c>
     </row>
@@ -628,7 +620,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Texting campaign log. Spend auto-calc at $0.07/msg. Enter Revenue from ActBlue ref codes.</t>
+          <t>Texting campaign log. Spend auto-calc at $0.07/msg.</t>
         </is>
       </c>
     </row>
@@ -640,7 +632,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Meta Ads Manager template. Paste data — CTR, CPC, CPR, ROAS auto-calculate.</t>
+          <t>Meta Ads Manager template. Paste data — CTR, CPC, ROAS auto-calculate.</t>
         </is>
       </c>
     </row>
@@ -652,7 +644,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Google Ads template with actual campaign data. Update Period tag each cycle.</t>
+          <t>Google Ads template with actual campaign data.</t>
         </is>
       </c>
     </row>
@@ -687,116 +679,116 @@
     <row r="15" ht="8" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>COLOR KEY</t>
+          <t>DASHBOARD DESIGN</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Yellow cells (#FFFF99)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Manual input required — fill these in</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Style</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Dark navy theme matching mgp.bluewavereporting.com — Sora/Inter fonts, period toggles, sidebar nav</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Black formula cells</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Auto-calculated — do not overwrite</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+          <t>Default password: pico — change via Vercel env var or by editing App.jsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="8" customHeight="1">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="8" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>COLOR KEY</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Yellow cells (#FFFF99)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Manual input required</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Blue header rows</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Column headers</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="8" customHeight="1">
-      <c r="A19" s="3" t="inlineStr"/>
-      <c r="B19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="8" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22" ht="8" customHeight="1">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="8" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>RATING SCALE (Email Open Rate)</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Excellent</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>≥ 25% open rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>20–24.9% open rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>≥ 14% open rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>15–19.9% open rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Below Avg</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>10–14.9% open rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>&lt; 10% open rate</t>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>10–13.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>&lt; 10%</t>
         </is>
       </c>
     </row>
@@ -821,182 +813,628 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>App.jsx Dashboard Code Block</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>PICO California Dashboard — App.jsx</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>Copy the code below into src/App.jsx in the pico-dashboard GitHub repo. Update DATA section each cycle.</t>
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Copy into src/App.jsx in the pico-dashboard GitHub repo. Matches MGP bluewavereporting.com design.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Code (copy all):</t>
         </is>
       </c>
     </row>
     <row r="4" ht="800" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">// ============================================================
-// PICO California Dashboard — App.jsx
-// Generated by BWPP Dashboard Builder
-// Update DATA INPUTS section each reporting period
-// ============================================================
-import React, { useState } from "react";
-// ── DATA INPUTS — update after each reporting cycle ──────────
-const DATA = {
-  period: "Current Period",
-  email: {
-    totalSends: 0,
-    avgOpenRate: 0,
-    avgClickRate: 0,
-    listSize180DO: 0,
-  },
-  finances: {
-    totalRaised: 634.0,
-    emailDigital: 275.0,
-    smsDigital: 0.0,
-    digitalTarget: 0.10,
-    byMonth: [
-      { month: "2026-03", total: 555.0, digital: 250.0 },
-      { month: "2026-04", total: 79.0, digital: 25.0 }
-    ],
-  },
-  texting: {
-    campaigns: [
-      { name: "251104 to OPT INS", date: "11/4/25", delivered: 8448, clicked: 0, revenue: 0 },
-      { name: "251104 to CA-22 ENGLISH", date: "11/4/25", delivered: 3685, clicked: 0, revenue: 0 },
-      { name: "251104 to CA-22 SPANISH", date: "11/4/25", delivered: 609, clicked: 0, revenue: 0 }
-    ],
-    costPerMsg: 0.07,
-  },
-  googleAds: {
-    period: "N/A",
-    campaigns: [
-      // Add Google Ads campaigns here
-    ],
-  },
-};
-// ── AUTO-COMPUTED ─────────────────────────────────────────────
-const totalDelivered = DATA.texting.campaigns.reduce((s,c) =&gt; s+c.delivered, 0);
-const totalSpend = totalDelivered * DATA.texting.costPerMsg;
-const totalRevenue = DATA.texting.campaigns.reduce((s,c) =&gt; s+c.revenue, 0);
-const textingROAS = totalSpend &gt; 0 ? totalRevenue / totalSpend : 0;
-const totalDigital = DATA.finances.emailDigital + DATA.finances.smsDigital;
-const digitalPct = DATA.finances.totalRaised &gt; 0 ? totalDigital / DATA.finances.totalRaised : 0;
-const emailRating = (rate) =&gt; {
-  if (rate &gt;= 0.25) return { label: "Excellent", color: "#22c55e" };
-  if (rate &gt;= 0.20) return { label: "Good", color: "#84cc16" };
-  if (rate &gt;= 0.15) return { label: "Average", color: "#f59e0b" };
-  if (rate &gt;= 0.10) return { label: "Below Avg", color: "#f97316" };
-  return { label: "Poor", color: "#ef4444" };
-};
-function KPICard({ title, value, sub, color }) {
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>import { useState } from "react";
+const PASSWORD = "pico";
+function PasswordGate({ children }) {
+  const [authed, setAuthed] = useState(() =&gt; sessionStorage.getItem("bwpp_auth") === "1");
+  const [input, setInput] = useState("");
+  const [error, setError] = useState(false);
+  if (authed) return children;
+  const handleSubmit = (e) =&gt; {
+    e.preventDefault();
+    if (input === PASSWORD) {
+      sessionStorage.setItem("bwpp_auth", "1");
+      setAuthed(true);
+    } else {
+      setError(true);
+      setInput("");
+    }
+  };
   return (
-    &lt;div style={{ border:"1px solid #e5e7eb", borderRadius:6, padding:16, background:"#fff", boxShadow:"0 1px 3px rgba(0,0,0,0.08)" }}&gt;
-      &lt;div style={{ fontSize:13, color:"#6b7280", marginBottom:4 }}&gt;{title}&lt;/div&gt;
-      &lt;div style={{ fontSize:28, fontWeight:"bold", color:color||"#1F4E79" }}&gt;{value}&lt;/div&gt;
-      {sub &amp;&amp; &lt;div style={{ fontSize:12, color:"#9ca3af", marginTop:4 }}&gt;{sub}&lt;/div&gt;}
+    &lt;div style={{ display: "flex", alignItems: "center", justifyContent: "center", minHeight: "100vh", background: "#060f1a" }}&gt;
+      &lt;div style={{ background: "#091929", border: "1px solid #1e3a5f", borderRadius: 12, padding: "40px 48px", minWidth: 320, textAlign: "center" }}&gt;
+        &lt;div style={{ fontSize: 22, fontWeight: 700, color: "#fff", marginBottom: 8 }}&gt;PICO California Dashboard&lt;/div&gt;
+        &lt;div style={{ fontSize: 14, color: "#64748b", marginBottom: 24 }}&gt;Enter password to continue&lt;/div&gt;
+        &lt;form onSubmit={handleSubmit}&gt;
+          &lt;input
+            type="password"
+            value={input}
+            onChange={(e) =&gt; { setInput(e.target.value); setError(false); }}
+            placeholder="Password"
+            autoFocus
+            style={{ width: "100%", padding: "10px 14px", borderRadius: 8, border: error ? "1px solid #ef4444" : "1px solid #1e3a5f", background: "#060f1a", color: "#fff", fontSize: 15, marginBottom: 8, boxSizing: "border-box", outline: "none" }}
+          /&gt;
+          {error &amp;&amp; &lt;div style={{ color: "#ef4444", fontSize: 13, marginBottom: 8 }}&gt;Incorrect password&lt;/div&gt;}
+          &lt;button type="submit" style={{ width: "100%", padding: "10px 0", borderRadius: 8, background: "#1d4ed8", color: "#fff", border: "none", fontSize: 15, fontWeight: 600, cursor: "pointer", marginTop: 4 }}&gt;Enter&lt;/button&gt;
+        &lt;/form&gt;
+      &lt;/div&gt;
     &lt;/div&gt;
   );
 }
-export default function App() {
-  const [tab, setTab] = useState("overview");
-  const rating = emailRating(DATA.email.avgOpenRate);
-  const TABS = ["overview","email","finances","texting","ads"];
+// ─── DATA (auto-generated — update weekly) ────────────────────────────────────
+const CLIENT = {
+  "name": "PICO California",
+  "cycle": "2025–2026",
+  "lastUpdated": "April 14, 2026",
+  "reportWeek": "Week of 4/13",
+  "reportMonth": "April 2026",
+  "reportQuarter": "Q2 2026"
+};
+const EMAIL_TOP_LINES = [];
+const EMAIL_MONTHLY_SUMMARY = {
+  "sends": 0,
+  "totalRecipients": 0,
+  "avgOpenRate": 0.0,
+  "avgClickRate": 0.0,
+  "totalUnsubs": 0
+};
+const EMAIL_QUARTERLY_SUMMARY = {
+  "sends": 0,
+  "totalRecipients": 0,
+  "avgOpenRate": 0.0,
+  "avgClickRate": 0.0,
+  "totalUnsubs": 0
+};
+const LIST_SIZE = [
+  {
+    "label": "30-Day Openers",
+    "key": "30DO",
+    "current": 0,
+    "prev": 0,
+    "change": 0.0,
+    "goal": null
+  },
+  {
+    "label": "90-Day Openers",
+    "key": "90DO",
+    "current": 0,
+    "prev": 0,
+    "change": 0.0,
+    "goal": null
+  },
+  {
+    "label": "180-Day Openers",
+    "key": "180DO",
+    "current": 0,
+    "prev": 0,
+    "change": 0.0,
+    "goal": null
+  },
+  {
+    "label": "Monthly New to List",
+    "key": "1MNTL",
+    "current": 0,
+    "prev": 0,
+    "change": 0.0,
+    "goal": null
+  },
+  {
+    "label": "All Subscribed",
+    "key": "ALL",
+    "current": 0,
+    "prev": 0,
+    "change": 0.0,
+    "goal": null
+  }
+];
+const FINANCES = [
+  {
+    "period": "Mar 2026",
+    "type": "month",
+    "totalActBlue": 555.0,
+    "digitalRaise": 250.0
+  },
+  {
+    "period": "Apr 2026",
+    "type": "month",
+    "totalActBlue": 79.0,
+    "digitalRaise": 25.0
+  },
+  {
+    "period": "Q2 2026 (QTD)",
+    "type": "qtd",
+    "totalActBlue": 634.0,
+    "digitalRaise": 275.0
+  }
+];
+const DIGITAL_PCT_MIN = 25;
+const DIGITAL_PCT_MAX = 30;
+const FINANCE_MONTHLY = {
+  "period": "April 2026 (MTD)",
+  "totalActBlue": 79.0,
+  "digitalRaise": 25.0,
+  "projection": 103
+};
+const FINANCE_QUARTERLY = {
+  "period": "Q2 2026 (QTD)",
+  "totalActBlue": 634.0,
+  "digitalRaise": 275.0,
+  "projection": 729
+};
+const ACQUISITION_ROI = [];
+const TEXTING_ROI = [
+  {
+    "campaign": "251104 to OPT INS",
+    "sendDate": "11/4",
+    "period": "monthly",
+    "sent": 8448,
+    "delivered": 8448,
+    "responses": 0,
+    "optOuts": 18,
+    "donations": 0,
+    "raised": 0
+  },
+  {
+    "campaign": "251104 to CA-22 ENGLISH",
+    "sendDate": "11/4",
+    "period": "monthly",
+    "sent": 3685,
+    "delivered": 3685,
+    "responses": 0,
+    "optOuts": 16,
+    "donations": 0,
+    "raised": 0
+  },
+  {
+    "campaign": "251104 to CA-22 SPANISH",
+    "sendDate": "11/4",
+    "period": "monthly",
+    "sent": 609,
+    "delivered": 609,
+    "responses": 0,
+    "optOuts": 3,
+    "donations": 0,
+    "raised": 0
+  }
+];
+const META_ADS = [];
+const GOOGLE_ADS = [];
+const GROWTH_CALC = [
+  {
+    "metric": "List Growth Rate (MoM)",
+    "value": "—",
+    "benchmark": "+1.5%",
+    "status": "above"
+  },
+  {
+    "metric": "Email Churn Rate",
+    "value": "—",
+    "benchmark": "&lt;0.15%",
+    "status": "above"
+  },
+  {
+    "metric": "Avg Open Rate (30d)",
+    "value": "0.0%",
+    "benchmark": "&gt;14% = Strong",
+    "status": "below"
+  },
+  {
+    "metric": "Avg Click Rate (30d)",
+    "value": "0.0%",
+    "benchmark": "&gt;3.0%",
+    "status": "below"
+  },
+  {
+    "metric": "SMS Opt-Out Rate",
+    "value": "—",
+    "benchmark": "&lt;0.20%",
+    "status": "above"
+  },
+  {
+    "metric": "Digital % of ActBlue",
+    "value": "43.4%",
+    "benchmark": "25–30%",
+    "status": "above"
+  }
+];
+const DEFAULT_HIGHLIGHTS = [
+  "Dashboard auto-generated for PICO California — April 14, 2026",
+  "Update this section with key insights for Week of 4/13",
+  "Add notable email performance observations here",
+  "Add texting campaign highlights here",
+  "Add fundraising milestones or anomalies here"
+];
+// ─── HELPERS ──────────────────────────────────────────────────────────────────
+const fmt = (n) =&gt; n?.toLocaleString() ?? "—";
+const fmtD = (n) =&gt; n != null ? `$${n.toLocaleString()}` : "—";
+const fmtP = (n) =&gt; n != null ? `${n}%` : "—";
+function openRateColor(r) {
+  if (r &gt;= 14) return "#4ade80";
+  if (r &gt;= 10) return "#fbbf24";
+  return "#f87171";
+}
+function openRateBadge(r) {
+  if (r &gt;= 14) return { label: "Strong",  color: "#4ade80", bg: "#052e16", border: "#166534" };
+  if (r &gt;= 10) return { label: "Average", color: "#fbbf24", bg: "#2d1f00", border: "#92400e" };
+  return           { label: "Low",     color: "#f87171", bg: "#3f0f0f", border: "#7f1d1d" };
+}
+function digitalPctStatus(p) {
+  if (p &gt;= DIGITAL_PCT_MIN &amp;&amp; p &lt;= DIGITAL_PCT_MAX) return { color: "#4ade80", label: "On Target",    bg: "#052e16", border: "#166534" };
+  if (p &gt; DIGITAL_PCT_MAX)                          return { color: "#60a5fa", label: "Above Target", bg: "#0c1f3f", border: "#1d4ed8" };
+  return                                                   { color: "#f87171", label: "Below Target", bg: "#3f0f0f", border: "#7f1d1d" };
+}
+function Delta({ val }) {
+  if (val == null) return null;
+  const up = val &gt;= 0;
+  return &lt;span style={{ color: up ? "#22c55e" : "#ef4444", fontWeight: 600, fontSize: 13 }}&gt;{up ? "▲" : "▼"} {Math.abs(val).toFixed(2)}%&lt;/span&gt;;
+}
+function GoalBar({ current, goal }) {
+  if (!goal) return null;
+  const pct = Math.min((current / goal) * 100, 100);
   return (
-    &lt;div style={{ fontFamily:"Arial,sans-serif", maxWidth:1100, margin:"0 auto", padding:20 }}&gt;
-      &lt;h1 style={{ background:"#1F4E79", color:"#fff", padding:"12px 20px", borderRadius:6, marginBottom:16 }}&gt;
-        PICO California — Digital Dashboard ({DATA.period})
-      &lt;/h1&gt;
-      &lt;div style={{ display:"flex", gap:8, marginBottom:20 }}&gt;
-        {TABS.map(t =&gt; (
-          &lt;button key={t} onClick={() =&gt; setTab(t)} style={{
-            padding:"8px 16px", borderRadius:4, border:"none", cursor:"pointer",
-            background: tab===t ? "#1F4E79" : "#e5e7eb",
-            color: tab===t ? "#fff" : "#374151",
-            fontWeight: tab===t ? "bold" : "normal",
-            textTransform:"capitalize"
-          }}&gt;{t}&lt;/button&gt;
-        ))}
+    &lt;div style={{ marginTop: 6 }}&gt;
+      &lt;div style={{ fontSize: 11, color: "#94a3b8", marginBottom: 3 }}&gt;{fmt(current)} / {fmt(goal)} goal ({pct.toFixed(1)}%)&lt;/div&gt;
+      &lt;div style={{ background: "#1e3a5f", borderRadius: 99, height: 6, overflow: "hidden" }}&gt;
+        &lt;div style={{ width: `${pct}%`, height: "100%", background: "linear-gradient(90deg,#1d4ed8,#60a5fa)", borderRadius: 99 }} /&gt;
       &lt;/div&gt;
-      {tab==="overview" &amp;&amp; (
-        &lt;div style={{ display:"grid", gridTemplateColumns:"1fr 1fr 1fr", gap:16 }}&gt;
-          &lt;KPICard title="Total Sends (Email)" value={DATA.email.totalSends} /&gt;
-          &lt;KPICard title="Avg Open Rate" value={(DATA.email.avgOpenRate*100).toFixed(1)+"%"} sub={rating.label} color={rating.color} /&gt;
-          &lt;KPICard title="Total Raised" value={"$"+DATA.finances.totalRaised.toLocaleString()} /&gt;
-          &lt;KPICard title="Digital Raised" value={"$"+totalDigital.toLocaleString()} sub={(digitalPct*100).toFixed(1)+"% of total (10% target)"} color={digitalPct&gt;=0.10?"#22c55e":"#ef4444"} /&gt;
-          &lt;KPICard title="Texts Delivered" value={totalDelivered.toLocaleString()} sub={DATA.texting.campaigns.length+" campaigns"} /&gt;
-          &lt;KPICard title="Texting Spend" value={"$"+totalSpend.toFixed(2)} sub="@ $0.07/msg" /&gt;
-        &lt;/div&gt;
-      )}
-      {tab==="email" &amp;&amp; (
-        &lt;div&gt;
-          &lt;h2&gt;Email Performance&lt;/h2&gt;
-          &lt;div style={{ display:"grid", gridTemplateColumns:"1fr 1fr 1fr", gap:12, marginBottom:16 }}&gt;
-            &lt;KPICard title="Total Sends" value={DATA.email.totalSends} /&gt;
-            &lt;KPICard title="Avg Open Rate" value={(DATA.email.avgOpenRate*100).toFixed(1)+"%"} color={rating.color} sub={rating.label} /&gt;
-            &lt;KPICard title="Avg Click Rate" value={(DATA.email.avgClickRate*100).toFixed(1)+"%"} /&gt;
+    &lt;/div&gt;
+  );
+}
+function DigitalPctBar({ pct }) {
+  const status = digitalPctStatus(pct);
+  const barWidth = Math.min(pct / 50 * 100, 100);
+  const minMark = DIGITAL_PCT_MIN / 50 * 100;
+  const maxMark = DIGITAL_PCT_MAX / 50 * 100;
+  return (
+    &lt;div style={{ marginTop: 10 }}&gt;
+      &lt;div style={{ display: "flex", justifyContent: "space-between", marginBottom: 4, fontSize: 12 }}&gt;
+        &lt;span style={{ color: "#94a3b8" }}&gt;Digital % of Total Raise&lt;/span&gt;
+        &lt;span style={{ color: status.color, fontWeight: 700 }}&gt;{pct.toFixed(1)}% — {status.label}&lt;/span&gt;
+      &lt;/div&gt;
+      &lt;div style={{ position: "relative", background: "#1e3a5f", borderRadius: 99, height: 10 }}&gt;
+        &lt;div style={{ position: "absolute", top: 0, bottom: 0, left: `${minMark}%`, width: `${maxMark - minMark}%`, background: "rgba(74,222,128,0.12)", borderLeft: "1px dashed #166534", borderRight: "1px dashed #166534" }} /&gt;
+        &lt;div style={{ width: `${barWidth}%`, height: "100%", background: `linear-gradient(90deg,#1d4ed8,${status.color})`, borderRadius: 99 }} /&gt;
+      &lt;/div&gt;
+      &lt;div style={{ display: "flex", justifyContent: "space-between", marginTop: 3, fontSize: 10, color: "#475569" }}&gt;
+        &lt;span&gt;0%&lt;/span&gt;
+        &lt;span style={{ color: "#4ade80" }}&gt;Target zone: {DIGITAL_PCT_MIN}–{DIGITAL_PCT_MAX}%&lt;/span&gt;
+        &lt;span&gt;50%&lt;/span&gt;
+      &lt;/div&gt;
+    &lt;/div&gt;
+  );
+}
+// ─── PERIOD TOGGLE ────────────────────────────────────────────────────────────
+function PeriodToggle({ active, onChange }) {
+  const options = [
+    { id: "weekly",    label: "Weekly",    sub: CLIENT.reportWeek },
+    { id: "monthly",   label: "Monthly",   sub: CLIENT.reportMonth },
+    { id: "quarterly", label: "Quarterly", sub: CLIENT.reportQuarter },
+  ];
+  return (
+    &lt;div style={{ display: "flex", gap: 8, marginBottom: 24 }}&gt;
+      {options.map(o =&gt; (
+        &lt;button key={o.id} onClick={() =&gt; onChange(o.id)} style={{
+          background: active === o.id ? "#1d4ed8" : "#091929",
+          border: `1px solid ${active === o.id ? "#3b82f6" : "#1e3a5f"}`,
+          borderRadius: 8, padding: "8px 18px", cursor: "pointer", textAlign: "left", transition: "all 0.15s",
+        }}&gt;
+          &lt;div style={{ fontSize: 13, fontWeight: 600, color: active === o.id ? "#fff" : "#94a3b8", fontFamily: "'Sora', sans-serif" }}&gt;{o.label}&lt;/div&gt;
+          &lt;div style={{ fontSize: 11, color: active === o.id ? "#93c5fd" : "#475569" }}&gt;{o.sub}&lt;/div&gt;
+        &lt;/button&gt;
+      ))}
+    &lt;/div&gt;
+  );
+}
+// ─── SUMMARY CALLOUT ──────────────────────────────────────────────────────────
+function SummaryCallout({ label, children }) {
+  return (
+    &lt;div style={{ background: "#091929", border: "1px solid #1e3a5f", borderRadius: 12, padding: "16px 22px", marginBottom: 20 }}&gt;
+      &lt;div style={{ fontSize: 11, color: "#64748b", textTransform: "uppercase", letterSpacing: "0.08em", marginBottom: 10 }}&gt;{label}&lt;/div&gt;
+      &lt;div style={{ display: "flex", flexWrap: "wrap", gap: 28 }}&gt;{children}&lt;/div&gt;
+    &lt;/div&gt;
+  );
+}
+function SummaryItem({ label, value, color }) {
+  return (
+    &lt;div&gt;
+      &lt;div style={{ fontSize: 22, fontWeight: 700, fontFamily: "'Sora', sans-serif", color: color || "#60a5fa", lineHeight: 1 }}&gt;{value}&lt;/div&gt;
+      &lt;div style={{ fontSize: 11, color: "#64748b", marginTop: 3 }}&gt;{label}&lt;/div&gt;
+    &lt;/div&gt;
+  );
+}
+// ─── SECTION ──────────────────────────────────────────────────────────────────
+function Section({ title, subtitle, children }) {
+  return (
+    &lt;div style={{ marginBottom: 48 }}&gt;
+      &lt;div style={{ marginBottom: 20 }}&gt;
+        &lt;h2 style={{ fontFamily: "'Sora', sans-serif", fontSize: 22, fontWeight: 700, color: "#e2e8f0", margin: 0, letterSpacing: "-0.2px" }}&gt;{title}&lt;/h2&gt;
+        {subtitle &amp;&amp; &lt;p style={{ margin: "4px 0 0", fontSize: 13, color: "#64748b" }}&gt;{subtitle}&lt;/p&gt;}
+      &lt;/div&gt;
+      {children}
+    &lt;/div&gt;
+  );
+}
+// ─── TABLE ────────────────────────────────────────────────────────────────────
+function Table({ headers, rows, alignRight = [] }) {
+  return (
+    &lt;div style={{ overflowX: "auto", borderRadius: 12, border: "1px solid #1e3a5f" }}&gt;
+      &lt;table style={{ width: "100%", borderCollapse: "collapse", fontSize: 13, fontFamily: "'Inter', sans-serif" }}&gt;
+        &lt;thead&gt;
+          &lt;tr style={{ background: "#0c2340" }}&gt;
+            {headers.map((h, i) =&gt; (
+              &lt;th key={i} style={{ padding: "10px 16px", textAlign: alignRight.includes(i) ? "right" : "left", color: "#94a3b8", fontWeight: 600, fontSize: 11, textTransform: "uppercase", letterSpacing: "0.06em", whiteSpace: "nowrap" }}&gt;{h}&lt;/th&gt;
+            ))}
+          &lt;/tr&gt;
+        &lt;/thead&gt;
+        &lt;tbody&gt;
+          {rows.map((row, ri) =&gt; (
+            &lt;tr key={ri} style={{ borderTop: "1px solid #1e3a5f", background: ri % 2 === 0 ? "#091929" : "#0b1f33" }}&gt;
+              {row.map((cell, ci) =&gt; (
+                &lt;td key={ci} style={{ padding: "10px 16px", textAlign: alignRight.includes(ci) ? "right" : "left", color: "#cbd5e1", whiteSpace: "nowrap" }}&gt;{cell}&lt;/td&gt;
+              ))}
+            &lt;/tr&gt;
+          ))}
+        &lt;/tbody&gt;
+      &lt;/table&gt;
+    &lt;/div&gt;
+  );
+}
+// ─── STAT CARD ────────────────────────────────────────────────────────────────
+function StatCard({ label, value, sub, accent }) {
+  return (
+    &lt;div style={{ background: "#091929", border: "1px solid #1e3a5f", borderRadius: 12, padding: "20px 24px", flex: "1 1 180px", minWidth: 160 }}&gt;
+      &lt;div style={{ fontSize: 11, color: "#64748b", textTransform: "uppercase", letterSpacing: "0.08em", marginBottom: 8 }}&gt;{label}&lt;/div&gt;
+      &lt;div style={{ fontSize: 26, fontWeight: 700, fontFamily: "'Sora', sans-serif", color: accent || "#60a5fa", lineHeight: 1 }}&gt;{value}&lt;/div&gt;
+      {sub &amp;&amp; &lt;div style={{ marginTop: 6, fontSize: 12, color: "#64748b" }}&gt;{sub}&lt;/div&gt;}
+    &lt;/div&gt;
+  );
+}
+// ─── EDITABLE HIGHLIGHTS ──────────────────────────────────────────────────────
+function EditableHighlights({ highlights, onChange }) {
+  const [editing, setEditing] = useState(false);
+  const [draft, setDraft] = useState(highlights.join("\n"));
+  const save = () =&gt; { onChange(draft.split("\n").map(s =&gt; s.trim()).filter(Boolean)); setEditing(false); };
+  const cancel = () =&gt; { setDraft(highlights.join("\n")); setEditing(false); };
+  return (
+    &lt;div style={{ background: "#091929", border: "1px solid #1e3a5f", borderRadius: 12, padding: "20px 24px" }}&gt;
+      &lt;div style={{ display: "flex", justifyContent: "space-between", alignItems: "center", marginBottom: 12 }}&gt;
+        &lt;div style={{ fontSize: 12, color: "#64748b", textTransform: "uppercase", letterSpacing: "0.06em" }}&gt;Highlights&lt;/div&gt;
+        {editing ? (
+          &lt;div style={{ display: "flex", gap: 8 }}&gt;
+            &lt;button onClick={save} style={{ background: "#1d4ed8", color: "#fff", border: "none", borderRadius: 6, padding: "5px 14px", fontSize: 12, cursor: "pointer", fontFamily: "'Inter', sans-serif", fontWeight: 600 }}&gt;Save&lt;/button&gt;
+            &lt;button onClick={cancel} style={{ background: "#1e3a5f", color: "#94a3b8", border: "none", borderRadius: 6, padding: "5px 14px", fontSize: 12, cursor: "pointer", fontFamily: "'Inter', sans-serif" }}&gt;Cancel&lt;/button&gt;
           &lt;/div&gt;
-        &lt;/div&gt;
-      )}
-      {tab==="finances" &amp;&amp; (
-        &lt;div&gt;
-          &lt;h2&gt;ActBlue Finances&lt;/h2&gt;
-          &lt;div style={{ display:"grid", gridTemplateColumns:"1fr 1fr 1fr", gap:12, marginBottom:16 }}&gt;
-            &lt;KPICard title="Total Raised" value={"$"+DATA.finances.totalRaised.toLocaleString()} /&gt;
-            &lt;KPICard title="Digital Raised" value={"$"+totalDigital.toLocaleString()} sub="Email + SMS" /&gt;
-            &lt;KPICard title="Digital %" value={(digitalPct*100).toFixed(1)+"%"} sub={digitalPct&gt;=0.10?"✓ Met 10% Target":"✗ Below 10% Target"} color={digitalPct&gt;=0.10?"#22c55e":"#ef4444"} /&gt;
-          &lt;/div&gt;
-          &lt;table style={{ width:"100%", borderCollapse:"collapse" }}&gt;
-            &lt;thead&gt;&lt;tr style={{ background:"#1F4E79", color:"#fff" }}&gt;
-              {["Month","Total Raised","Digital Raised","Digital %","Status"].map(h =&gt; (
-                &lt;th key={h} style={{ padding:"8px", textAlign:h==="Month"?"left":"right" }}&gt;{h}&lt;/th&gt;
-              ))}
-            &lt;/tr&gt;&lt;/thead&gt;
-            &lt;tbody&gt;
-              {DATA.finances.byMonth.map((m,i) =&gt; {
-                const pct = m.total&gt;0 ? m.digital/m.total : 0;
-                return (
-                  &lt;tr key={m.month} style={{ background:i%2===0?"#D6E4F0":"#fff" }}&gt;
-                    &lt;td style={{ padding:"6px 8px" }}&gt;{m.month}&lt;/td&gt;
-                    &lt;td style={{ padding:"6px 8px", textAlign:"right" }}&gt;${"$"+m.total.toLocaleString()}&lt;/td&gt;
-                    &lt;td style={{ padding:"6px 8px", textAlign:"right" }}&gt;${"$"+m.digital.toLocaleString()}&lt;/td&gt;
-                    &lt;td style={{ padding:"6px 8px", textAlign:"right" }}&gt;{(pct*100).toFixed(1)+"%"}&lt;/td&gt;
-                    &lt;td style={{ padding:"6px 8px", textAlign:"right", color:pct&gt;=0.10?"#22c55e":"#ef4444" }}&gt;{pct&gt;=0.10?"✓ Met":"✗ Below"}&lt;/td&gt;
-                  &lt;/tr&gt;
-                );
-              })}
-            &lt;/tbody&gt;
-          &lt;/table&gt;
-        &lt;/div&gt;
-      )}
-      {tab==="texting" &amp;&amp; (
-        &lt;div&gt;
-          &lt;h2&gt;Texting ROI&lt;/h2&gt;
-          &lt;div style={{ display:"grid", gridTemplateColumns:"1fr 1fr 1fr", gap:12, marginBottom:16 }}&gt;
-            &lt;KPICard title="Total Delivered" value={totalDelivered.toLocaleString()} /&gt;
-            &lt;KPICard title="Total Spend" value={"$"+totalSpend.toFixed(2)} sub="@ $0.07/msg" /&gt;
-            &lt;KPICard title="ROAS" value={totalRevenue&gt;0?textingROAS.toFixed(2)+"x":"—"} sub="Enter revenue to calculate" /&gt;
-          &lt;/div&gt;
-        &lt;/div&gt;
-      )}
-      {tab==="ads" &amp;&amp; (
-        &lt;div&gt;
-          &lt;h2&gt;Google Ads — {DATA.googleAds.period}&lt;/h2&gt;
-        &lt;/div&gt;
+        ) : (
+          &lt;button onClick={() =&gt; { setDraft(highlights.join("\n")); setEditing(true); }} style={{ background: "transparent", color: "#60a5fa", border: "1px solid #1e4976", borderRadius: 6, padding: "5px 14px", fontSize: 12, cursor: "pointer", fontFamily: "'Inter', sans-serif" }}&gt;Edit&lt;/button&gt;
+        )}
+      &lt;/div&gt;
+      {editing ? (
+        &lt;textarea value={draft} onChange={e =&gt; setDraft(e.target.value)} style={{ width: "100%", background: "#060f1a", border: "1px solid #1e4976", borderRadius: 8, color: "#e2e8f0", padding: "12px", fontSize: 13, fontFamily: "'Inter', sans-serif", lineHeight: 1.9, resize: "vertical", minHeight: 140, outline: "none", boxSizing: "border-box" }} placeholder="One highlight per line..." /&gt;
+      ) : (
+        &lt;ul style={{ margin: 0, paddingLeft: 20, color: "#94a3b8", fontSize: 13, lineHeight: 2.1 }}&gt;
+          {highlights.map((h, i) =&gt; &lt;li key={i}&gt;{h}&lt;/li&gt;)}
+        &lt;/ul&gt;
       )}
     &lt;/div&gt;
   );
 }
-</t>
+// ─── NAV ──────────────────────────────────────────────────────────────────────
+const NAV_ITEMS = [
+  { id: "overview",    label: "Digital Overview" },
+  { id: "email",       label: "Email" },
+  { id: "listsize",    label: "List Size" },
+  { id: "finances",    label: "Finances" },
+  { id: "acquisition", label: "Acquisition ROI" },
+  { id: "texting",     label: "Texting ROI" },
+  { id: "ads",         label: "Ad Reporting" },
+  { id: "growth",      label: "Growth" },
+];
+// ─── MAIN APP ─────────────────────────────────────────────────────────────────
+export default function Dashboard() {
+  const [active, setActive] = useState("overview");
+  const [period, setPeriod] = useState("weekly");
+  const [highlights, setHighlights] = useState(DEFAULT_HIGHLIGHTS);
+  const scrollTo = (id) =&gt; {
+    setActive(id);
+    document.getElementById(id)?.scrollIntoView({ behavior: "smooth", block: "start" });
+  };
+  const emailRows   = period === "weekly"    ? EMAIL_TOP_LINES.filter(r =&gt; r.period === "weekly")
+                    : period === "monthly"   ? EMAIL_TOP_LINES.filter(r =&gt; ["weekly","monthly"].includes(r.period))
+                    : EMAIL_TOP_LINES;
+  const textingRows = TEXTING_ROI.filter(r =&gt; period === "weekly" ? r.period === "weekly" : period === "monthly" ? ["weekly","monthly"].includes(r.period) : true);
+  const metaRows    = META_ADS.filter(r =&gt; period === "weekly" ? r.period === "weekly" : period === "monthly" ? ["weekly","monthly"].includes(r.period) : true);
+  const googleRows  = GOOGLE_ADS.filter(r =&gt; period === "weekly" ? r.period === "weekly" : period === "monthly" ? ["weekly","monthly"].includes(r.period) : true);
+  const acquisRows  = ACQUISITION_ROI.filter(r =&gt; period === "weekly" ? r.period === "weekly" : period === "monthly" ? ["weekly","monthly"].includes(r.period) : true);
+  const financeRows = period === "quarterly" ? FINANCES : FINANCES.filter(r =&gt; r.type === "month");
+  const totalActBlue = FINANCES.filter(r =&gt; r.type === "month").reduce((s, r) =&gt; s + r.totalActBlue, 0);
+  const totalDigital = FINANCES.filter(r =&gt; r.type === "month").reduce((s, r) =&gt; s + r.digitalRaise, 0);
+  const overallPct   = totalActBlue &gt; 0 ? (totalDigital / totalActBlue) * 100 : 0;
+  const overallStatus = digitalPctStatus(overallPct);
+  const periodLabel = period === "weekly" ? CLIENT.reportWeek : period === "monthly" ? CLIENT.reportMonth : CLIENT.reportQuarter;
+  const initials = CLIENT.name.split(" ").map(w =&gt; w[0]).join("").slice(0, 2).toUpperCase();
+  return (
+    &lt;PasswordGate&gt;
+      &lt;div style={{ minHeight: "100vh", background: "#060f1a", color: "#e2e8f0", fontFamily: "'Inter', sans-serif" }}&gt;
+        &lt;style&gt;{`
+          @import url('https://fonts.googleapis.com/css2?family=Sora:wght@600;700;800&amp;family=Inter:wght@300;400;500;600&amp;display=swap');
+          * { box-sizing: border-box; }
+          ::-webkit-scrollbar { width: 6px; height: 6px; }
+          ::-webkit-scrollbar-track { background: #060f1a; }
+          ::-webkit-scrollbar-thumb { background: #1e3a5f; border-radius: 3px; }
+          .nav-item { cursor: pointer; transition: color 0.15s; }
+          .nav-item:hover { color: #60a5fa !important; }
+          .badge-above { background: #052e16; color: #4ade80; border: 1px solid #166534; }
+          .badge-below { background: #3f0f0f; color: #f87171; border: 1px solid #7f1d1d; }
+        `}&lt;/style&gt;
+        {/* HEADER */}
+        &lt;header style={{ position: "sticky", top: 0, zIndex: 100, background: "rgba(6,15,26,0.96)", backdropFilter: "blur(12px)", borderBottom: "1px solid #1e3a5f", padding: "0 32px", display: "flex", alignItems: "center", justifyContent: "space-between", height: 64 }}&gt;
+          &lt;div style={{ display: "flex", alignItems: "center", gap: 14 }}&gt;
+            &lt;div style={{ width: 36, height: 36, borderRadius: 8, background: "linear-gradient(135deg,#1d4ed8,#3b82f6)", display: "flex", alignItems: "center", justifyContent: "center", fontSize: 15, fontWeight: 800, fontFamily: "'Sora', sans-serif", color: "#fff", flexShrink: 0 }}&gt;{initials}&lt;/div&gt;
+            &lt;div&gt;
+              &lt;div style={{ fontFamily: "'Sora', sans-serif", fontWeight: 700, fontSize: 15, color: "#e2e8f0", lineHeight: 1.1 }}&gt;{CLIENT.name}&lt;/div&gt;
+              &lt;div style={{ fontSize: 11, color: "#475569", letterSpacing: "0.06em" }}&gt;{CLIENT.cycle} CAMPAIGN REPORT&lt;/div&gt;
+            &lt;/div&gt;
+          &lt;/div&gt;
+          &lt;div style={{ display: "flex", alignItems: "center", gap: 16 }}&gt;
+            &lt;div style={{ display: "flex", background: "#091929", border: "1px solid #1e3a5f", borderRadius: 8, overflow: "hidden" }}&gt;
+              {["weekly","monthly","quarterly"].map(p =&gt; (
+                &lt;button key={p} onClick={() =&gt; setPeriod(p)} style={{ background: period === p ? "#1d4ed8" : "transparent", border: "none", color: period === p ? "#fff" : "#64748b", padding: "6px 14px", fontSize: 12, fontWeight: 600, cursor: "pointer", fontFamily: "'Inter', sans-serif", textTransform: "capitalize", transition: "all 0.15s" }}&gt;{p}&lt;/button&gt;
+              ))}
+            &lt;/div&gt;
+            &lt;div style={{ fontSize: 12, color: "#475569" }}&gt;Updated &lt;span style={{ color: "#60a5fa" }}&gt;{CLIENT.lastUpdated}&lt;/span&gt;&lt;/div&gt;
+          &lt;/div&gt;
+        &lt;/header&gt;
+        &lt;div style={{ display: "flex" }}&gt;
+          {/* SIDEBAR */}
+          &lt;nav style={{ width: 200, flexShrink: 0, position: "sticky", top: 64, height: "calc(100vh - 64px)", overflowY: "auto", borderRight: "1px solid #1e3a5f", padding: "24px 0", background: "#07121e" }}&gt;
+            {NAV_ITEMS.map(item =&gt; (
+              &lt;div key={item.id} className="nav-item" onClick={() =&gt; scrollTo(item.id)} style={{ padding: "9px 24px", fontSize: 13, fontWeight: active === item.id ? 600 : 400, color: active === item.id ? "#60a5fa" : "#64748b", borderLeft: active === item.id ? "2px solid #3b82f6" : "2px solid transparent" }}&gt;
+                {item.label}
+              &lt;/div&gt;
+            ))}
+            &lt;div style={{ margin: "24px 24px 0", padding: "12px 16px", background: "#0c2340", borderRadius: 8, border: "1px solid #1e3a5f" }}&gt;
+              &lt;div style={{ fontSize: 10, color: "#475569", textTransform: "uppercase", letterSpacing: "0.08em", marginBottom: 4 }}&gt;Viewing&lt;/div&gt;
+              &lt;div style={{ fontSize: 12, color: "#94a3b8", textTransform: "capitalize", fontWeight: 600 }}&gt;{period}&lt;/div&gt;
+              &lt;div style={{ fontSize: 11, color: "#475569", marginTop: 2 }}&gt;{periodLabel}&lt;/div&gt;
+            &lt;/div&gt;
+          &lt;/nav&gt;
+          &lt;main style={{ flex: 1, padding: "40px 48px", maxWidth: "calc(100% - 200px)", overflowX: "hidden" }}&gt;
+            {/* DIGITAL OVERVIEW */}
+            &lt;div id="overview"&gt;
+              &lt;Section title="Digital Overview" subtitle={`${periodLabel} · ${CLIENT.lastUpdated}`}&gt;
+                &lt;PeriodToggle active={period} onChange={setPeriod} /&gt;
+                {period === "monthly" &amp;&amp; (
+                  &lt;SummaryCallout label={`${CLIENT.reportMonth} — Monthly Summary`}&gt;
+                    &lt;SummaryItem label="Email Sends" value={EMAIL_MONTHLY_SUMMARY.sends} color="#60a5fa" /&gt;
+                    &lt;SummaryItem label="Avg Open Rate" value={`${EMAIL_MONTHLY_SUMMARY.avgOpenRate}%`} color="#fbbf24" /&gt;
+                    &lt;SummaryItem label="Digital Raised (MTD)" value={fmtD(FINANCE_MONTHLY.digitalRaise)} color="#4ade80" /&gt;
+                    &lt;SummaryItem label="% to Projection" value={FINANCE_MONTHLY.projection &gt; 0 ? `${((FINANCE_MONTHLY.totalActBlue / FINANCE_MONTHLY.projection) * 100).toFixed(1)}%` : "—"} color="#a78bfa" /&gt;
+                  &lt;/SummaryCallout&gt;
+                )}
+                {period === "quarterly" &amp;&amp; (
+                  &lt;SummaryCallout label={`${CLIENT.reportQuarter} — Quarterly Summary`}&gt;
+                    &lt;SummaryItem label="Email Sends" value={EMAIL_QUARTERLY_SUMMARY.sends} color="#60a5fa" /&gt;
+                    &lt;SummaryItem label="Avg Open Rate" value={`${EMAIL_QUARTERLY_SUMMARY.avgOpenRate}%`} color="#fbbf24" /&gt;
+                    &lt;SummaryItem label="Digital Raised (QTD)" value={fmtD(FINANCE_QUARTERLY.digitalRaise)} color="#4ade80" /&gt;
+                    &lt;SummaryItem label="Total ActBlue (QTD)" value={fmtD(FINANCE_QUARTERLY.totalActBlue)} color="#a78bfa" /&gt;
+                    &lt;SummaryItem label="% to Q Projection" value={FINANCE_QUARTERLY.projection &gt; 0 ? `${((FINANCE_QUARTERLY.totalActBlue / FINANCE_QUARTERLY.projection) * 100).toFixed(1)}%` : "—"} color="#fb923c" /&gt;
+                  &lt;/SummaryCallout&gt;
+                )}
+                &lt;div style={{ display: "flex", flexWrap: "wrap", gap: 16, marginBottom: 24 }}&gt;
+                  &lt;StatCard label="Total Subscribers" value={fmt(LIST_SIZE.find(r =&gt; r.key === "ALL")?.current || 0)} sub={LIST_SIZE.find(r =&gt; r.key === "ALL")?.goal ? `Goal: ${fmt(LIST_SIZE.find(r =&gt; r.key === "ALL").goal)}` : null} /&gt;
+                  &lt;StatCard label="Avg Open Rate" value={`${EMAIL_MONTHLY_SUMMARY.avgOpenRate}%`} sub="14%+ = Strong" accent="#fbbf24" /&gt;
+                  &lt;StatCard label={period === "quarterly" ? "Digital Raised (QTD)" : "Digital Raised (MTD)"} value={period === "quarterly" ? fmtD(FINANCE_QUARTERLY.digitalRaise) : fmtD(FINANCE_MONTHLY.digitalRaise)} sub={`${((period === "quarterly" ? FINANCE_QUARTERLY.digitalRaise / (FINANCE_QUARTERLY.totalActBlue || 1) : FINANCE_MONTHLY.digitalRaise / (FINANCE_MONTHLY.totalActBlue || 1)) * 100).toFixed(1)}% of ActBlue`} accent="#34d399" /&gt;
+                  &lt;StatCard label="SMS List" value={fmt(LIST_SIZE.find(r =&gt; r.key === "180DO")?.current || 0)} sub="180-Day Openers" accent="#fb923c" /&gt;
+                  &lt;StatCard label="Total Ad Spend" value={fmtD(META_ADS.reduce((s,r) =&gt; s + (r.spend||0), 0) + GOOGLE_ADS.reduce((s,r) =&gt; s + (r.spend||0), 0))} sub="Meta + Google" accent="#f472b6" /&gt;
+                &lt;/div&gt;
+                &lt;EditableHighlights highlights={highlights} onChange={setHighlights} /&gt;
+              &lt;/Section&gt;
+            &lt;/div&gt;
+            {/* EMAIL */}
+            &lt;div id="email"&gt;
+              &lt;Section title="Email" subtitle="Broadcast performance from EveryAction"&gt;
+                &lt;PeriodToggle active={period} onChange={setPeriod} /&gt;
+                {period === "monthly" &amp;&amp; (
+                  &lt;SummaryCallout label={`${CLIENT.reportMonth} — Email Summary`}&gt;
+                    &lt;SummaryItem label="Total Sends" value={EMAIL_MONTHLY_SUMMARY.sends} /&gt;
+                    &lt;SummaryItem label="Total Recipients" value={fmt(EMAIL_MONTHLY_SUMMARY.totalRecipients)} /&gt;
+                    &lt;SummaryItem label="Avg Open Rate" value={`${EMAIL_MONTHLY_SUMMARY.avgOpenRate}%`} color={openRateColor(EMAIL_MONTHLY_SUMMARY.avgOpenRate)} /&gt;
+                    &lt;SummaryItem label="Avg Click Rate" value={`${EMAIL_MONTHLY_SUMMARY.avgClickRate}%`} color="#a78bfa" /&gt;
+                    &lt;SummaryItem label="Total Unsubs" value={EMAIL_MONTHLY_SUMMARY.totalUnsubs} color="#f87171" /&gt;
+                  &lt;/SummaryCallout&gt;
+                )}
+                {period === "quarterly" &amp;&amp; (
+                  &lt;SummaryCallout label={`${CLIENT.reportQuarter} — Email Summary`}&gt;
+                    &lt;SummaryItem label="Total Sends" value={EMAIL_QUARTERLY_SUMMARY.sends} /&gt;
+                    &lt;SummaryItem label="Total Recipients" value={fmt(EMAIL_QUARTERLY_SUMMARY.totalRecipients)} /&gt;
+                    &lt;SummaryItem label="Avg Open Rate" value={`${EMAIL_QUARTERLY_SUMMARY.avgOpenRate}%`} color={openRateColor(EMAIL_QUARTERLY_SUMMARY.avgOpenRate)} /&gt;
+                    &lt;SummaryItem label="Avg Click Rate" value={`${EMAIL_QUARTERLY_SUMMARY.avgClickRate}%`} color="#a78bfa" /&gt;
+                    &lt;SummaryItem label="Total Unsubs" value={EMAIL_QUARTERLY_SUMMARY.totalUnsubs} color="#f87171" /&gt;
+                  &lt;/SummaryCallout&gt;
+                )}
+                {emailRows.length &gt; 0 ? (
+                  &lt;Table
+                    headers={["Subject Line", "Date", "Recipients", "Opens", "Open Rate", "Rating", "Clicks", "Click Rate", "Unsubs"]}
+                    alignRight={[2,3,4,6,7,8]}
+                    rows={emailRows.map(r =&gt; {
+                      const badge = openRateBadge(r.openRate);
+                      return [
+                        &lt;span style={{ color: "#e2e8f0" }}&gt;{r.subject}&lt;/span&gt;,
+                        r.sendDate, fmt(r.recipients), fmt(r.opens),
+                        &lt;span style={{ color: openRateColor(r.openRate), fontWeight: 600 }}&gt;{fmtP(r.openRate)}&lt;/span&gt;,
+                        &lt;span style={{ padding: "2px 9px", borderRadius: 10, fontSize: 11, fontWeight: 600, background: badge.bg, color: badge.color, border: `1px solid ${badge.border}` }}&gt;{badge.label}&lt;/span&gt;,
+                        fmt(r.clicks), fmtP(r.clickRate), fmt(r.unsubs),
+                      ];
+                    })}
+                  /&gt;
+                ) : &lt;div style={{ color: "#475569", fontSize: 13, padding: "20px 0" }}&gt;No sends recorded for this period yet.&lt;/div&gt;}
+                &lt;div style={{ display: "flex", gap: 20, marginTop: 12, flexWrap: "wrap" }}&gt;
+                  {[["Strong","≥14%","#4ade80","#052e16","#166534"],["Average","10–13.9%","#fbbf24","#2d1f00","#92400e"],["Low","&lt;10%","#f87171","#3f0f0f","#7f1d1d"]].map(([label,range,color,bg,border]) =&gt; (
+                    &lt;div key={label} style={{ display: "flex", alignItems: "center", gap: 7, fontSize: 12 }}&gt;
+                      &lt;span style={{ padding: "2px 9px", borderRadius: 10, fontWeight: 600, background: bg, color, border: `1px solid ${border}`, fontSize: 11 }}&gt;{label}&lt;/span&gt;
+                      &lt;span style={{ color: "#475569" }}&gt;{range} open rate&lt;/span&gt;
+                    &lt;/div&gt;
+                  ))}
+                &lt;/div&gt;
+              &lt;/Section&gt;
+            &lt;/div&gt;
+            {/* LIST SIZE */}
+            &lt;div id="listsize"&gt;
+              &lt;Section title="List Size" subtitle="Subscriber segment counts — week-over-week"&gt;
+                &lt;div style={{ display: "flex", flexDirection: "column", gap: 12 }}&gt;
+                  {LIST_SIZE.map(row =&gt; (
+                    &lt;div key={row.key} style={{ background: "#091929", border: "1px solid #1e3a5f", borderRadius: 12, padding: "18px 24px", display: "flex", alignItems: "center", gap: 24 }}&gt;
+                      &lt;div style={{ minWidth: 160 }}&gt;
+                        &lt;div style={{ fontSize: 11, color: "#64748b", textTransform: "uppercase", letterSpacing: "0.06em" }}&gt;{row.key}&lt;/div&gt;
+                        &lt;div style={{ fontFamily: "'Sora', sans-serif", fontWeight: 600, fontSize: 14, color: "#e2e8f0", marginTop: 2 }}&gt;{row.label}&lt;/div&gt;
+                      &lt;/div&gt;
+                      &lt;div style={{ flex: 1 }}&gt;
+                        &lt;div style={{ fontSize: 28, fontWeight: 700, fontFamily: "'Sora', sans-serif", color: "#60a5fa", lineHeight: 1 }}&gt;{fmt(row.current)}&lt;/div&gt;
+                        &lt;div style={{ fontSize: 12, color: "#475569", marginTop: 2 }}&gt;prev: {fmt(row.prev)} &amp;nbsp; &lt;Delta val={row.change} /&gt;&lt;/div&gt;
+                        &lt;GoalBar current={row.current} goal={row.goal} /&gt;
+                      &lt;/div&gt;
+                    &lt;/div&gt;
+                  ))}
+                &lt;/div&gt;
+              &lt;/Section&gt;
+            &lt;/div&gt;
+            {/* FINANCES */}
+            &lt;div id="finances"&gt;
+              &lt;Section title="Finances" subtitle="ActBlue fundraising — digital raise target: 25–30% of total"&gt;
+                &lt;PeriodToggle active={period} onChange={setPeriod} /&gt;
+                &lt;div style={{ display: "flex", flexWrap: "wrap", gap: 16, marginBottom: 20 }}&gt;
+                  {period === "quarterly" ? (
+                    &lt;&gt;
+                      &lt;StatCard label="Total ActBlue (QTD)" value={fmtD(FINANCE_QUARTERLY.totalActBlue)} accent="#60a5fa" /&gt;
+                      &lt;StatCard label="Digital Raise (QTD)" value={fmtD(FINANCE_QUARTERLY.digitalRaise)} sub="Email + SMS + Ads" accent="#4ade80" /&gt;
+                      {FINANCE_QUARTERLY.projection &gt; 0 &amp;&amp; &lt;StatCard label="Q Projection" value={fmtD(FINANCE_QUARTERLY.projection)} sub={`${((FINANCE_QUARTERLY.totalActBlue/FINANCE_QUARTERLY.projection)*100).toFixed(1)}% to goal`} accent="#a78bfa" /&gt;}
+                    &lt;/&gt;
+                  ) : (
+                    &lt;&gt;
+                      &lt;StatCard label="Total ActBlue (MTD)" value={fmtD(FINANCE_MONTHLY.totalActBlue)} accent="#60a5fa" /&gt;
+                      &lt;StatCard label="Digital Raise (MTD)" value={fmtD(FINANCE_MONTHLY.digitalRaise)} sub="Email + SMS + Ads" accent="#4ade80" /&gt;
+                      {FINANCE_MONTHLY.projection &gt; 0 &amp;&amp; &lt;StatCard label="Monthly Projection" value={fmtD(FINANCE_MONTHLY.projection)} sub={`${((FINANCE_MONTHLY.totalActBlue/FINANCE_MONTHLY.projection)*100).toFixed(1)}% to goal`} accent="#a78bfa" /&gt;}
+                    &lt;/&gt;
+                  )}
+                  {overallPct &gt; 0 &amp;&amp; (
+                    &lt;div style={{ background: "#091929", border: "1px solid #1e3a5f", borderRadius: 12, padding: "20px 24px", flex: "2 1 260px", minWidth: 220 }}&gt;
+                      &lt;div style={{ fontSize: 11, color: "#64748b", textTransform: "uppercase", letterSpacing: "0.08em", marginBottom: 6 }}&gt;Digital % of ActBlue&lt;/div&gt;
+                      &lt;div style={{ display: "flex", alignItems: "baseline", gap: 10 }}&gt;
+                        &lt;div style={{ fontSize: 26, fontWeight: 700, fontFamily: "'Sora', sans-serif", color: overallStatus.color }}&gt;{overallPct.toFixed(1)}%&lt;/div&gt;
+                        &lt;span style={{ padding</t>
         </is>
       </c>
     </row>
